--- a/Examples/Powder_Raman/Castep/results.ref.xlsx
+++ b/Examples/Powder_Raman/Castep/results.ref.xlsx
@@ -238,13 +238,13 @@
     <t>Raman electro-optic term</t>
   </si>
   <si>
-    <t>Raman laser frequency</t>
-  </si>
-  <si>
     <t>Raman laser polarisation</t>
   </si>
   <si>
     <t>HV</t>
+  </si>
+  <si>
+    <t>Raman laser wavelength</t>
   </si>
   <si>
     <t>Raman orientation samples</t>
@@ -2037,8 +2037,8 @@
       <c r="B21" t="s">
         <v>72</v>
       </c>
-      <c r="C21">
-        <v>785</v>
+      <c r="C21" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2046,10 +2046,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
         <v>74</v>
+      </c>
+      <c r="C22">
+        <v>785</v>
       </c>
     </row>
     <row r="23" spans="1:3">

--- a/Examples/Powder_Raman/Castep/results.ref.xlsx
+++ b/Examples/Powder_Raman/Castep/results.ref.xlsx
@@ -130,13 +130,13 @@
     <t>Absorption maximum (L/mole/cm)</t>
   </si>
   <si>
-    <t>Raman R_total (Å4/amu)</t>
+    <t>Raman R_total (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_parallel (Å4/amu)</t>
+    <t>Raman R_parallel (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_perp (Å4/amu)</t>
+    <t>Raman R_perp (Å⁴/amu)</t>
   </si>
   <si>
     <t>No</t>
@@ -1142,13 +1142,13 @@
         <v>7.150450744208263E-09</v>
       </c>
       <c r="I26">
-        <v>0.01709544008466918</v>
+        <v>0.0053450484758727</v>
       </c>
       <c r="J26">
-        <v>0.009768863530108928</v>
+        <v>0.003054326116438643</v>
       </c>
       <c r="K26">
-        <v>0.007326576554560253</v>
+        <v>0.002290722359434057</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1174,13 +1174,13 @@
         <v>8.767200466440267E-10</v>
       </c>
       <c r="I27">
-        <v>0.02488206716197894</v>
+        <v>0.00777960991363805</v>
       </c>
       <c r="J27">
-        <v>0.01421872945951975</v>
+        <v>0.004445618120975269</v>
       </c>
       <c r="K27">
-        <v>0.01066333770245919</v>
+        <v>0.003333991792662781</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1206,13 +1206,13 @@
         <v>7.225511154712662E-09</v>
       </c>
       <c r="I28">
-        <v>0.01697526373077348</v>
+        <v>0.005307474220162125</v>
       </c>
       <c r="J28">
-        <v>0.009700187036019225</v>
+        <v>0.003032853771284356</v>
       </c>
       <c r="K28">
-        <v>0.007275076694754254</v>
+        <v>0.002274620448877769</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1238,13 +1238,13 @@
         <v>1.20317879414898E-07</v>
       </c>
       <c r="I29">
-        <v>1.524116977317211</v>
+        <v>0.4765293602454055</v>
       </c>
       <c r="J29">
-        <v>0.8709239870384353</v>
+        <v>0.2723024915688122</v>
       </c>
       <c r="K29">
-        <v>0.653192990278776</v>
+        <v>0.2042268686765933</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1270,13 +1270,13 @@
         <v>3.850221860597329E-07</v>
       </c>
       <c r="I30">
-        <v>1.524116977943524</v>
+        <v>0.476529360441228</v>
       </c>
       <c r="J30">
-        <v>0.8709239873963979</v>
+        <v>0.2723024916807325</v>
       </c>
       <c r="K30">
-        <v>0.6531929905471261</v>
+        <v>0.2042268687604955</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1302,13 +1302,13 @@
         <v>1.416963080219959E-06</v>
       </c>
       <c r="I31">
-        <v>9.006738396367854E-15</v>
+        <v>2.816040599110539E-15</v>
       </c>
       <c r="J31">
-        <v>5.268306038717794E-15</v>
+        <v>1.647184923184995E-15</v>
       </c>
       <c r="K31">
-        <v>3.738432357650061E-15</v>
+        <v>1.168855675925544E-15</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1334,13 +1334,13 @@
         <v>9348.998534569953</v>
       </c>
       <c r="I32">
-        <v>43.49071061903597</v>
+        <v>13.59777550958538</v>
       </c>
       <c r="J32">
-        <v>40.99294947153823</v>
+        <v>12.81682723633798</v>
       </c>
       <c r="K32">
-        <v>2.497761147497743</v>
+        <v>0.7809482732474042</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -1366,13 +1366,13 @@
         <v>8941.435632425737</v>
       </c>
       <c r="I33">
-        <v>0.0009960465562963016</v>
+        <v>0.0003114232275543565</v>
       </c>
       <c r="J33">
-        <v>0.0005725454844787231</v>
+        <v>0.0001790116752785552</v>
       </c>
       <c r="K33">
-        <v>0.0004235010718175785</v>
+        <v>0.0001324115522758013</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -1398,13 +1398,13 @@
         <v>8941.378765585836</v>
       </c>
       <c r="I34">
-        <v>0.0007270109322463511</v>
+        <v>0.0002273067353692139</v>
       </c>
       <c r="J34">
-        <v>0.0004154375704876047</v>
+        <v>0.0001298904235256485</v>
       </c>
       <c r="K34">
-        <v>0.0003115733617587465</v>
+        <v>9.741631184356541E-05</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -1430,13 +1430,13 @@
         <v>7.344586784170893E-07</v>
       </c>
       <c r="I35">
-        <v>6.443298091213503</v>
+        <v>2.014557125845448</v>
       </c>
       <c r="J35">
-        <v>3.681884623550574</v>
+        <v>1.151175500483113</v>
       </c>
       <c r="K35">
-        <v>2.76141346766293</v>
+        <v>0.8633816253623349</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -1462,13 +1462,13 @@
         <v>1.768507732370293E-06</v>
       </c>
       <c r="I36">
-        <v>6.443298095262342</v>
+        <v>2.014557127111356</v>
       </c>
       <c r="J36">
-        <v>3.681884625864206</v>
+        <v>1.151175501206492</v>
       </c>
       <c r="K36">
-        <v>2.761413469398137</v>
+        <v>0.8633816259048636</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -1494,13 +1494,13 @@
         <v>3.363913119295343E-07</v>
       </c>
       <c r="I37">
-        <v>4.338382834602092E-14</v>
+        <v>1.356435777201048E-14</v>
       </c>
       <c r="J37">
-        <v>2.479507466608996E-14</v>
+        <v>7.752410900026187E-15</v>
       </c>
       <c r="K37">
-        <v>1.858875367993095E-14</v>
+        <v>5.811946871984293E-15</v>
       </c>
     </row>
   </sheetData>
